--- a/Deliverables/BOM/Sensor-Board/Client_BOM-Sensor-Board.xlsx
+++ b/Deliverables/BOM/Sensor-Board/Client_BOM-Sensor-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Sensor-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A8CDE1-AEF6-4F51-901C-6861A782CA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD50CD5-4EEA-4916-A38F-A3DB68EB00AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
   <si>
     <t>Component list</t>
   </si>
@@ -65,18 +65,9 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>C1, C22, C46, C48, C50, C54, C56, C58, C60, C65, C66, C67, C68, C73, C74, C75, C76</t>
-  </si>
-  <si>
-    <t>C16, C45, C47, C49, C53, C55, C57, C59</t>
-  </si>
-  <si>
     <t>C51, C52</t>
   </si>
   <si>
-    <t>C61, C62, C63, C64, C69, C70, C71, C72</t>
-  </si>
-  <si>
     <t>J1</t>
   </si>
   <si>
@@ -86,21 +77,9 @@
     <t>P1, P2, P3, P4, P5, P6, P7, P8, P9, P10, P11, P12, P13, P14, P15, P16, P17, P18, P19</t>
   </si>
   <si>
-    <t>R17, R18, R19, R20, R21, R22, R23, R24</t>
-  </si>
-  <si>
     <t>R25, R26</t>
   </si>
   <si>
-    <t>R27, R28, R29, R30, R35, R36, R37, R38</t>
-  </si>
-  <si>
-    <t>R31, R32, R33, R34, R39, R40, R41, R42</t>
-  </si>
-  <si>
-    <t>U8, U9, U10, U11, U12, U13, U14, U15</t>
-  </si>
-  <si>
     <t>U16</t>
   </si>
   <si>
@@ -113,15 +92,9 @@
     <t>CAP CER 0.1UF 50V X7R 0402</t>
   </si>
   <si>
-    <t>CAP CER 10UF 25V X5R 0603</t>
-  </si>
-  <si>
     <t>CAP CER 1UF 16V X5R 0402</t>
   </si>
   <si>
-    <t>Cap Ceramic 0.022uF 25V X7R 10% Pad SMD 0402</t>
-  </si>
-  <si>
     <t>CONN FFC BOTTOM 24POS 0.50MM R/A</t>
   </si>
   <si>
@@ -131,21 +104,9 @@
     <t>Test Point ON</t>
   </si>
   <si>
-    <t>RES SMD 0402 240 Ohm 1% 1/16W ±100ppm/°C Molded SMD Paper T/R</t>
-  </si>
-  <si>
     <t>1/10W Thin Film Resistor 75V ±0.5% ±25ppm/℃ -55℃~+155℃ 64kΩ 0603 Chip Resistor - Surface Mount ROHS</t>
   </si>
   <si>
-    <t>Res Thick Film 0402 6.8K Ohm 5% 0.063W(1/16W) ±100ppm/C Pad SMD T/R</t>
-  </si>
-  <si>
-    <t>RES SMD 0402 150kOhm 5% Paper T/R</t>
-  </si>
-  <si>
-    <t>IC OPAMP INSTR 825KHZ 8SOIC</t>
-  </si>
-  <si>
     <t>SOT-23-5 Operational Amplifier ROHS</t>
   </si>
   <si>
@@ -158,24 +119,15 @@
     <t>Cap 0402</t>
   </si>
   <si>
-    <t>Cap0603</t>
-  </si>
-  <si>
     <t>FH12-24S-0.5SH(55)</t>
   </si>
   <si>
     <t>FH34SRJ-12S-0.5SH(50)</t>
   </si>
   <si>
-    <t>Res0402</t>
-  </si>
-  <si>
     <t>Res0603</t>
   </si>
   <si>
-    <t>SOIC-8</t>
-  </si>
-  <si>
     <t>SOT-23-5</t>
   </si>
   <si>
@@ -188,27 +140,9 @@
     <t>GRM155R71H104ME14D</t>
   </si>
   <si>
-    <t>CL10A106MA8NRNC</t>
-  </si>
-  <si>
     <t>CC0402KRX5R7BB105</t>
   </si>
   <si>
-    <t>CGA2B2X7R1E223K050BA</t>
-  </si>
-  <si>
-    <t>RC0402FR-07240RL</t>
-  </si>
-  <si>
-    <t>RC0402JR-076K8L</t>
-  </si>
-  <si>
-    <t>RC0402JR-07150KL</t>
-  </si>
-  <si>
-    <t>AD8221ARZ-R7</t>
-  </si>
-  <si>
     <t>TPMCP6021T-E/OT</t>
   </si>
   <si>
@@ -221,24 +155,15 @@
     <t>Murata</t>
   </si>
   <si>
-    <t>Samsung</t>
-  </si>
-  <si>
     <t>Yageo</t>
   </si>
   <si>
-    <t>TDK</t>
-  </si>
-  <si>
     <t>Hirose</t>
   </si>
   <si>
     <t>iking Tech</t>
   </si>
   <si>
-    <t>Analog Devices</t>
-  </si>
-  <si>
     <t>TECH PUBLIC</t>
   </si>
   <si>
@@ -251,27 +176,12 @@
     <t>0.1uF</t>
   </si>
   <si>
-    <t>10uF'</t>
-  </si>
-  <si>
     <t>1uF</t>
   </si>
   <si>
-    <t>22nF</t>
-  </si>
-  <si>
-    <t>240R</t>
-  </si>
-  <si>
     <t>64K</t>
   </si>
   <si>
-    <t>6K8</t>
-  </si>
-  <si>
-    <t>150K</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
@@ -279,6 +189,15 @@
   </si>
   <si>
     <t>----------</t>
+  </si>
+  <si>
+    <t>C1, C60</t>
+  </si>
+  <si>
+    <t>ARG03DTC6402N</t>
+  </si>
+  <si>
+    <t>Quantity 5 Boards</t>
   </si>
 </sst>
 </file>
@@ -288,7 +207,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,6 +332,12 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -450,7 +375,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -517,21 +442,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -625,21 +535,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top/>
       <bottom style="medium">
@@ -665,6 +560,129 @@
       </right>
       <top/>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -673,21 +691,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -696,10 +710,10 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -713,110 +727,168 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -846,16 +918,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>10417</xdr:rowOff>
+      <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1733550</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -883,7 +955,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13315950" y="600967"/>
+          <a:off x="13554075" y="629542"/>
           <a:ext cx="1714500" cy="1104008"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1160,571 +1232,450 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
     <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.5703125" customWidth="1"/>
     <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="22"/>
+      <c r="B1" s="19"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="40"/>
-    </row>
-    <row r="2" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
+    </row>
+    <row r="2" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="12" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="35" t="s">
+      <c r="D2" s="10"/>
+      <c r="E2" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F2" s="11"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="38"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="14" t="s">
+      <c r="B3" s="21"/>
+      <c r="C3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="36" t="s">
+      <c r="D3" s="12"/>
+      <c r="E3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="41"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F3" s="12"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="34"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="14" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="37" t="s">
+      <c r="D4" s="12"/>
+      <c r="E4" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="42"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F4" s="13"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="35"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="14" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="38" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="42"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F5" s="14"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="35"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="42"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="22"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="35"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="42"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="23"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="35"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="42"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="46"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="35"/>
+    </row>
+    <row r="9" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="52" t="s">
+      <c r="D9" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="52" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" s="53" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="J9" s="50" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="54">
+      <c r="B10" s="52">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="59" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="67">
+        <v>2</v>
+      </c>
+      <c r="J10" s="49">
+        <f>I10*5</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="52">
+        <f>ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="33" t="s">
+      <c r="D11" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="I10" s="49">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="54">
-        <f t="shared" ref="B11:B23" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="H11" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="68">
         <v>2</v>
       </c>
-      <c r="C11" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="I11" s="50">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J11" s="31">
+        <f t="shared" ref="J11:J17" si="0">I11*5</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="54">
+      <c r="B12" s="52">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="69">
+        <v>1</v>
+      </c>
+      <c r="J12" s="30">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="52">
+        <f t="shared" ref="B13:B17" si="1">ROW(B13) - ROW($B$9)</f>
+        <v>4</v>
+      </c>
+      <c r="C13" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="I12" s="49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="54">
+      <c r="D13" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="71" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="68">
+        <v>1</v>
+      </c>
+      <c r="J13" s="31">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="I13" s="50">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="54">
+      <c r="B14" s="52">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="69">
+        <v>19</v>
+      </c>
+      <c r="J14" s="30">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="52">
+        <f>ROW(B15) - ROW($B$9)</f>
+        <v>6</v>
+      </c>
+      <c r="C15" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="F14" s="33" t="s">
+      <c r="D15" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="I14" s="49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="54">
+      <c r="H15" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" s="68">
+        <v>2</v>
+      </c>
+      <c r="J15" s="31">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="F15" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="I15" s="50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="54">
+      <c r="B16" s="52">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="61" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="69">
+        <v>1</v>
+      </c>
+      <c r="J16" s="30">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="52">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="F16" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="H16" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="I16" s="49">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="54">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="34" t="s">
+      <c r="D17" s="62" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="F17" s="62" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="H17" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="I17" s="50">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="54">
-        <f>ROW(B18) - ROW($B$9)</f>
-        <v>9</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="H18" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="I18" s="49">
+      <c r="H17" s="72" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="70">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="54">
+      <c r="J17" s="40">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="H19" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="I19" s="50">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="54">
-        <f>ROW(B20) - ROW($B$9)</f>
-        <v>11</v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="H20" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="I20" s="49">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="54">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C21" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="H21" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="I21" s="50">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="54">
-        <f>ROW(B22) - ROW($B$9)</f>
-        <v>13</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="H22" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="I22" s="49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="54">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C23" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="I23" s="50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="30" t="s">
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="31"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="44"/>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="10" t="s">
+      <c r="D18" s="43"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="45"/>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="46"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="I3:I8"/>
-    <mergeCell ref="E24:I25"/>
+    <mergeCell ref="J3:J8"/>
+    <mergeCell ref="E18:J19"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Deliverables/BOM/Sensor-Board/Client_BOM-Sensor-Board.xlsx
+++ b/Deliverables/BOM/Sensor-Board/Client_BOM-Sensor-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Sensor-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD50CD5-4EEA-4916-A38F-A3DB68EB00AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410452D1-C5EC-4045-92FB-C92B84368B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
   <si>
     <t>Component list</t>
   </si>
@@ -74,9 +74,6 @@
     <t>J2</t>
   </si>
   <si>
-    <t>P1, P2, P3, P4, P5, P6, P7, P8, P9, P10, P11, P12, P13, P14, P15, P16, P17, P18, P19</t>
-  </si>
-  <si>
     <t>R25, R26</t>
   </si>
   <si>
@@ -95,9 +92,6 @@
     <t>CAP CER 1UF 16V X5R 0402</t>
   </si>
   <si>
-    <t>CONN FFC BOTTOM 24POS 0.50MM R/A</t>
-  </si>
-  <si>
     <t>CONN FPC/FFC 12POS .5MM</t>
   </si>
   <si>
@@ -119,9 +113,6 @@
     <t>Cap 0402</t>
   </si>
   <si>
-    <t>FH12-24S-0.5SH(55)</t>
-  </si>
-  <si>
     <t>FH34SRJ-12S-0.5SH(50)</t>
   </si>
   <si>
@@ -198,6 +189,54 @@
   </si>
   <si>
     <t>Quantity 5 Boards</t>
+  </si>
+  <si>
+    <t>Slide Lock 32 Bottom Contact Surface Mount 0.5mm SMD,P=0.5mm FFC/FPC Connectors ROHS</t>
+  </si>
+  <si>
+    <t>AFC07-S32FCA-00</t>
+  </si>
+  <si>
+    <t>JUSHUO</t>
+  </si>
+  <si>
+    <t>P1, P3, P5, P7, P9, P11, P13, P15, P16, P18, P20</t>
+  </si>
+  <si>
+    <t>R1, R2</t>
+  </si>
+  <si>
+    <t>RES SMD 10K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>Res0402</t>
+  </si>
+  <si>
+    <t>RC0402FR-0710KL</t>
+  </si>
+  <si>
+    <t>10K</t>
+  </si>
+  <si>
+    <t>SW1, SW2</t>
+  </si>
+  <si>
+    <t>No Gull Wing 50mA 100MΩ 80000 260gf@±50gf 12V -25℃~+85℃ 1.7mm Golden Round Button Brick nogging SPST SMD Tactile Switches ROHS</t>
+  </si>
+  <si>
+    <t>TC-0522C-1.7-260G</t>
+  </si>
+  <si>
+    <t>HCTL</t>
+  </si>
+  <si>
+    <t>-----</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>DO NOT MOUNT</t>
   </si>
 </sst>
 </file>
@@ -207,7 +246,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,6 +377,39 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -375,7 +447,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -547,17 +619,6 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -634,17 +695,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -663,35 +713,70 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -767,31 +852,7 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -806,12 +867,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -819,17 +874,14 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -846,50 +898,134 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -916,25 +1052,20 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1733550</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="1714500" cy="1104008"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A1056AA-F661-4692-ABD4-D7F92465C1C9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -955,7 +1086,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13554075" y="629542"/>
+          <a:off x="11144250" y="629542"/>
           <a:ext cx="1714500" cy="1104008"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -964,7 +1095,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1232,7 +1363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -1241,11 +1372,12 @@
     <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="2"/>
@@ -1253,10 +1385,10 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
-    </row>
-    <row r="2" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H1" s="67"/>
+      <c r="I1" s="68"/>
+    </row>
+    <row r="2" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="10" t="s">
@@ -1269,10 +1401,11 @@
       <c r="F2" s="11"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="38"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="76"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="12" t="s">
@@ -1286,9 +1419,10 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="34"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J3" s="4"/>
+      <c r="K3" s="69"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="12" t="s">
@@ -1302,9 +1436,10 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="35"/>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J4" s="6"/>
+      <c r="K4" s="70"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="12" t="s">
@@ -1318,9 +1453,10 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="35"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J5" s="5"/>
+      <c r="K5" s="70"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="15"/>
@@ -1330,9 +1466,10 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="35"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J6" s="5"/>
+      <c r="K6" s="70"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="17"/>
@@ -1342,340 +1479,423 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="35"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J7" s="7"/>
+      <c r="K7" s="70"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="48"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="38"/>
       <c r="F8" s="17"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="35"/>
-    </row>
-    <row r="9" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="7"/>
+      <c r="K8" s="70"/>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="50" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9" s="40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="52">
+      <c r="B10" s="66">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="59" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="63" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="63" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="59" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="67">
+      <c r="C10" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="62">
         <v>2</v>
       </c>
-      <c r="J10" s="49">
+      <c r="J10" s="39">
         <f>I10*5</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="39"/>
+    </row>
+    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="52">
-        <f>ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="66">
+        <f t="shared" ref="B11:B19" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="60" t="s">
+      <c r="D11" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="63">
+        <v>2</v>
+      </c>
+      <c r="J11" s="31">
+        <f t="shared" ref="J11:K19" si="1">I11*5</f>
+        <v>10</v>
+      </c>
+      <c r="K11" s="31"/>
+    </row>
+    <row r="12" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="66">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="64">
+        <v>1</v>
+      </c>
+      <c r="J12" s="30">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="K12" s="30"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="66">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="55" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="60" t="s">
+      <c r="E13" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="68">
-        <v>2</v>
-      </c>
-      <c r="J11" s="31">
-        <f t="shared" ref="J11:J17" si="0">I11*5</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="52">
-        <f>ROW(B12) - ROW($B$9)</f>
-        <v>3</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="56" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="I12" s="69">
+      <c r="F13" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="63">
         <v>1</v>
       </c>
-      <c r="J12" s="30">
+      <c r="J13" s="31">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="K13" s="31"/>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="66">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="52">
-        <f t="shared" ref="B13:B17" si="1">ROW(B13) - ROW($B$9)</f>
-        <v>4</v>
-      </c>
-      <c r="C13" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="60" t="s">
+      <c r="C14" s="77" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="78" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="79" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="81" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="82" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="83">
+        <v>11</v>
+      </c>
+      <c r="J14" s="84">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="K14" s="85" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="66">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="63">
+        <v>2</v>
+      </c>
+      <c r="J15" s="31">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="K15" s="31"/>
+    </row>
+    <row r="16" spans="1:11" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="66">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="55" t="s">
+      <c r="E16" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="60" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" s="71" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" s="68">
+      <c r="G16" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="65">
+        <v>2</v>
+      </c>
+      <c r="J16" s="55">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="K16" s="55"/>
+    </row>
+    <row r="17" spans="1:11" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="66">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="54" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" s="63">
+        <v>2</v>
+      </c>
+      <c r="J17" s="31">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="K17" s="31"/>
+    </row>
+    <row r="18" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="66">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" s="65">
         <v>1</v>
       </c>
-      <c r="J13" s="31">
-        <f t="shared" si="0"/>
+      <c r="J18" s="55">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="52">
-        <f>ROW(B14) - ROW($B$9)</f>
-        <v>5</v>
-      </c>
-      <c r="C14" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="69">
-        <v>19</v>
-      </c>
-      <c r="J14" s="30">
-        <f t="shared" si="0"/>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="52">
-        <f>ROW(B15) - ROW($B$9)</f>
-        <v>6</v>
-      </c>
-      <c r="C15" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="55" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="60" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="I15" s="68">
-        <v>2</v>
-      </c>
-      <c r="J15" s="31">
+      <c r="K18" s="55"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="86">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="52">
-        <f>ROW(B16) - ROW($B$9)</f>
-        <v>7</v>
-      </c>
-      <c r="C16" s="56" t="s">
+      <c r="C19" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="61" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="56" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" s="69">
-        <v>1</v>
-      </c>
-      <c r="J16" s="30">
-        <f t="shared" si="0"/>
+      <c r="D19" s="87" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="88" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" s="89">
+        <v>2</v>
+      </c>
+      <c r="J19" s="32">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="K19" s="32"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="34" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="52">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="C17" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="62" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="62" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="72" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" s="70">
-        <v>2</v>
-      </c>
-      <c r="J17" s="40">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="42" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="43"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="45"/>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="8" t="s">
+      <c r="D20" s="35"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+    </row>
+    <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="37"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="73"/>
+      <c r="K21" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J3:J8"/>
-    <mergeCell ref="E18:J19"/>
-    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K3:K8"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="E20:K21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
